--- a/rubrics/Dataset_Channel_Registry_Batch2.xlsx
+++ b/rubrics/Dataset_Channel_Registry_Batch2.xlsx
@@ -530,7 +530,7 @@
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -579,7 +579,7 @@
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -628,7 +628,7 @@
       </c>
       <c r="K4" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -677,7 +677,7 @@
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -726,7 +726,7 @@
       </c>
       <c r="K6" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -775,7 +775,7 @@
       </c>
       <c r="K7" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -824,7 +824,7 @@
       </c>
       <c r="K8" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -873,7 +873,7 @@
       </c>
       <c r="K9" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -922,7 +922,7 @@
       </c>
       <c r="K10" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -971,7 +971,7 @@
       </c>
       <c r="K11" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1020,7 +1020,7 @@
       </c>
       <c r="K12" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1069,7 +1069,7 @@
       </c>
       <c r="K13" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1118,7 +1118,7 @@
       </c>
       <c r="K14" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1167,7 +1167,7 @@
       </c>
       <c r="K15" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1216,7 +1216,7 @@
       </c>
       <c r="K16" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1265,7 +1265,7 @@
       </c>
       <c r="K17" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1314,7 +1314,7 @@
       </c>
       <c r="K18" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1363,7 +1363,7 @@
       </c>
       <c r="K19" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1412,7 +1412,7 @@
       </c>
       <c r="K20" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1461,7 +1461,7 @@
       </c>
       <c r="K21" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1510,7 +1510,7 @@
       </c>
       <c r="K22" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1559,7 +1559,7 @@
       </c>
       <c r="K23" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1608,7 +1608,7 @@
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1657,7 +1657,7 @@
       </c>
       <c r="K25" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1706,7 +1706,7 @@
       </c>
       <c r="K26" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1755,7 +1755,7 @@
       </c>
       <c r="K27" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1804,7 +1804,7 @@
       </c>
       <c r="K28" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="K29" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1902,7 +1902,7 @@
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -1951,7 +1951,7 @@
       </c>
       <c r="K31" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2000,7 +2000,7 @@
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2049,7 +2049,7 @@
       </c>
       <c r="K33" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2098,7 +2098,7 @@
       </c>
       <c r="K34" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2147,7 +2147,7 @@
       </c>
       <c r="K35" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2196,7 +2196,7 @@
       </c>
       <c r="K36" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2245,7 +2245,7 @@
       </c>
       <c r="K37" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2294,7 +2294,7 @@
       </c>
       <c r="K38" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2343,7 +2343,7 @@
       </c>
       <c r="K39" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2392,7 +2392,7 @@
       </c>
       <c r="K40" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2441,7 +2441,7 @@
       </c>
       <c r="K41" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2490,7 +2490,7 @@
       </c>
       <c r="K42" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2539,7 +2539,7 @@
       </c>
       <c r="K43" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2588,7 +2588,7 @@
       </c>
       <c r="K44" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2637,7 +2637,7 @@
       </c>
       <c r="K45" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2735,7 +2735,7 @@
       </c>
       <c r="K47" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2817,7 +2817,7 @@
       </c>
       <c r="K49" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2866,7 +2866,7 @@
       </c>
       <c r="K50" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2915,7 +2915,7 @@
       </c>
       <c r="K51" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>
@@ -2964,7 +2964,7 @@
       </c>
       <c r="K52" t="inlineStr">
         <is>
-          <t>Pending</t>
+          <t>Yes</t>
         </is>
       </c>
     </row>

--- a/rubrics/Dataset_Channel_Registry_Batch2.xlsx
+++ b/rubrics/Dataset_Channel_Registry_Batch2.xlsx
@@ -521,8 +521,6 @@
           <t>Threat briefings, ransomware family deep dives</t>
         </is>
       </c>
-      <c r="H2" t="inlineStr"/>
-      <c r="I2" t="inlineStr"/>
       <c r="J2" t="inlineStr">
         <is>
           <t>SentinelLabs publishes detailed ransomware family reports; strong RaaS and affiliate model coverage.</t>
@@ -547,7 +545,7 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@CheckPointSoftware</t>
+          <t>https://www.youtube.com/channel/UCXnlgfiXZQm1sbxMzU-8ZKA</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
@@ -570,8 +568,6 @@
           <t>Threat briefings, actor profiling, family breakdowns</t>
         </is>
       </c>
-      <c r="H3" t="inlineStr"/>
-      <c r="I3" t="inlineStr"/>
       <c r="J3" t="inlineStr">
         <is>
           <t>CPR produces frequent RaaS and ransomware group analyses; technically detailed.</t>
@@ -619,8 +615,6 @@
           <t>Threat briefings, attribution research, affiliate tracking</t>
         </is>
       </c>
-      <c r="H4" t="inlineStr"/>
-      <c r="I4" t="inlineStr"/>
       <c r="J4" t="inlineStr">
         <is>
           <t>Strong ransomware attribution and affiliate tracking content; vendor bias but technically solid.</t>
@@ -668,8 +662,6 @@
           <t>IR case studies, adversary simulation research</t>
         </is>
       </c>
-      <c r="H5" t="inlineStr"/>
-      <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr">
         <is>
           <t>Formerly F-Secure; deep IR and adversary simulation research with strong technical credibility.</t>
@@ -694,7 +686,7 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Rapid7</t>
+          <t>https://www.youtube.com/channel/UCnctXOUIeRFu1BR5O0W5e9w</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
@@ -717,8 +709,6 @@
           <t>Threat briefings, exploitation research, vulnerability analysis</t>
         </is>
       </c>
-      <c r="H6" t="inlineStr"/>
-      <c r="I6" t="inlineStr"/>
       <c r="J6" t="inlineStr">
         <is>
           <t>Strong on initial access exploitation used by ransomware operators; AttackerKB content relevant.</t>
@@ -766,8 +756,6 @@
           <t>Ransomware family analyses, threat intel reports</t>
         </is>
       </c>
-      <c r="H7" t="inlineStr"/>
-      <c r="I7" t="inlineStr"/>
       <c r="J7" t="inlineStr">
         <is>
           <t>Ransomware-focused vendor; Malwarebytes ThreatDown publishes regular family breakdowns.</t>
@@ -815,8 +803,6 @@
           <t>Actor attribution, ransomware affiliate profiling, dark web intel</t>
         </is>
       </c>
-      <c r="H8" t="inlineStr"/>
-      <c r="I8" t="inlineStr"/>
       <c r="J8" t="inlineStr">
         <is>
           <t>Strong CIS/Russia-nexus ransomware actor coverage; unique dark web and affiliate intel perspective.</t>
@@ -841,7 +827,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Prodaft</t>
+          <t>https://www.youtube.com/channel/UCdVNTCZJ_KctZPiINLX1wvg</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -864,8 +850,6 @@
           <t>Threat actor deep dives, ransomware group infiltration reports</t>
         </is>
       </c>
-      <c r="H9" t="inlineStr"/>
-      <c r="I9" t="inlineStr"/>
       <c r="J9" t="inlineStr">
         <is>
           <t>Publishes rare inside-access reports on ransomware group infrastructure; highly technical.</t>
@@ -913,8 +897,6 @@
           <t>Threat briefings, IOC analysis, weekly threat roundups</t>
         </is>
       </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
       <c r="J10" t="inlineStr">
         <is>
           <t>Regular threat intelligence briefings; useful for IOC and campaign tracking context.</t>
@@ -962,8 +944,6 @@
           <t>Incident response case studies, ransomware trends</t>
         </is>
       </c>
-      <c r="H11" t="inlineStr"/>
-      <c r="I11" t="inlineStr"/>
       <c r="J11" t="inlineStr">
         <is>
           <t>Major IR consulting firm; quarterly threat landscape reports with strong ransomware focus.</t>
@@ -1011,8 +991,6 @@
           <t>Technical research talks, malware analysis</t>
         </is>
       </c>
-      <c r="H12" t="inlineStr"/>
-      <c r="I12" t="inlineStr"/>
       <c r="J12" t="inlineStr">
         <is>
           <t>Research-oriented security consultancy; publishes detailed vulnerability and malware research.</t>
@@ -1060,8 +1038,6 @@
           <t>Ransomware family analyses, decryptor releases, trend reports</t>
         </is>
       </c>
-      <c r="H13" t="inlineStr"/>
-      <c r="I13" t="inlineStr"/>
       <c r="J13" t="inlineStr">
         <is>
           <t>Exclusively ransomware-focused vendor; one of the leading sources for family-level technical detail and decryptor development.</t>
@@ -1109,8 +1085,6 @@
           <t>Malware genetic analysis, code reuse tracking, family lineage</t>
         </is>
       </c>
-      <c r="H14" t="inlineStr"/>
-      <c r="I14" t="inlineStr"/>
       <c r="J14" t="inlineStr">
         <is>
           <t>Unique code-similarity approach to malware attribution; valuable for ransomware lineage and shared tooling across families.</t>
@@ -1158,8 +1132,6 @@
           <t>Dark web monitoring, ransomware leak site tracking, actor intelligence</t>
         </is>
       </c>
-      <c r="H15" t="inlineStr"/>
-      <c r="I15" t="inlineStr"/>
       <c r="J15" t="inlineStr">
         <is>
           <t>Specialises in external threat intelligence including ransomware extortion sites and threat actor communications.</t>
@@ -1184,7 +1156,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@ReliaQuest</t>
+          <t>https://www.youtube.com/channel/UCdPuTyaN5bU3_GmCNFgzl3Q</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -1207,8 +1179,6 @@
           <t>MDR case studies, threat briefings, ransomware trend reports</t>
         </is>
       </c>
-      <c r="H16" t="inlineStr"/>
-      <c r="I16" t="inlineStr"/>
       <c r="J16" t="inlineStr">
         <is>
           <t>MDR platform vendor with regular ransomware coverage; useful for detection and response perspectives.</t>
@@ -1256,8 +1226,6 @@
           <t>Threat intel reports, IR case studies, active defence content</t>
         </is>
       </c>
-      <c r="H17" t="inlineStr"/>
-      <c r="I17" t="inlineStr"/>
       <c r="J17" t="inlineStr">
         <is>
           <t>Practitioner-heavy MDR firm; publishes threat intel alongside IR and detection content.</t>
@@ -1305,8 +1273,6 @@
           <t>Memory forensics, disk triage, DFIR walkthroughs</t>
         </is>
       </c>
-      <c r="H18" t="inlineStr"/>
-      <c r="I18" t="inlineStr"/>
       <c r="J18" t="inlineStr">
         <is>
           <t>Richard Davis; one of the highest-quality practitioner DFIR channels. Deep technical walkthroughs of tools and artefacts used in ransomware intrusions.</t>
@@ -1331,7 +1297,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@HuskyHacks</t>
+          <t>https://www.youtube.com/channel/UCtJgZIyoZ0wIKEzctj_8pZQ</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -1354,8 +1320,6 @@
           <t>Malware analysis, offensive tool walkthroughs</t>
         </is>
       </c>
-      <c r="H19" t="inlineStr"/>
-      <c r="I19" t="inlineStr"/>
       <c r="J19" t="inlineStr">
         <is>
           <t>Well-structured malware analysis content; useful for understanding attacker tooling used alongside ransomware.</t>
@@ -1403,8 +1367,6 @@
           <t>Attack chain walkthroughs, red team techniques, IR fundamentals</t>
         </is>
       </c>
-      <c r="H20" t="inlineStr"/>
-      <c r="I20" t="inlineStr"/>
       <c r="J20" t="inlineStr">
         <is>
           <t>The Cyber Mentor; large audience with solid coverage of techniques used in ransomware intrusion chains (credential access, lateral movement).</t>
@@ -1452,8 +1414,6 @@
           <t>Malware reverse engineering, unpacking, analysis walkthroughs</t>
         </is>
       </c>
-      <c r="H21" t="inlineStr"/>
-      <c r="I21" t="inlineStr"/>
       <c r="J21" t="inlineStr">
         <is>
           <t>Detailed static and dynamic malware analysis; useful for ransomware encryption and dropper analysis.</t>
@@ -1501,8 +1461,6 @@
           <t>Live malware detonations, ransomware behaviour analysis</t>
         </is>
       </c>
-      <c r="H22" t="inlineStr"/>
-      <c r="I22" t="inlineStr"/>
       <c r="J22" t="inlineStr">
         <is>
           <t>Interactive sandbox vendor; publishes ransomware execution walkthroughs with process tree and network activity detail.</t>
@@ -1550,8 +1508,6 @@
           <t>Cloud IR case studies, ransomware in cloud environments</t>
         </is>
       </c>
-      <c r="H23" t="inlineStr"/>
-      <c r="I23" t="inlineStr"/>
       <c r="J23" t="inlineStr">
         <is>
           <t>Cloud-native DFIR vendor; unique coverage of ransomware targeting AWS, Azure, and GCP environments.</t>
@@ -1599,16 +1555,14 @@
           <t>ATT&amp;CK detection engineering, threat hunting, Jupyter-based analysis</t>
         </is>
       </c>
-      <c r="H24" t="inlineStr"/>
-      <c r="I24" t="inlineStr"/>
       <c r="J24" t="inlineStr">
         <is>
-          <t>Roberto Rodriguez; MITRE ATT&amp;CK contributor. Excellent detection-layer content aligned with ransomware tactic coverage.</t>
+          <t>Roberto Rodriguez; MITRE ATT&amp;CK contributor. Excellent detection-layer content aligned with ransomware tactic coverage. [EXCLUDED: no dedicated YouTube channel found via API handle lookup or name search as of 2026-08-11 — likely hosted only on other platforms/conference archives.]</t>
         </is>
       </c>
       <c r="K24" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1648,8 +1602,6 @@
           <t>Research talks, malware family analyses, threat actor profiling</t>
         </is>
       </c>
-      <c r="H25" t="inlineStr"/>
-      <c r="I25" t="inlineStr"/>
       <c r="J25" t="inlineStr">
         <is>
           <t>Dedicated anti-malware/threat intelligence conference; among the highest ransomware content density of any conference channel.</t>
@@ -1697,8 +1649,6 @@
           <t>Exploitation research, malware RE, adversary technique talks</t>
         </is>
       </c>
-      <c r="H26" t="inlineStr"/>
-      <c r="I26" t="inlineStr"/>
       <c r="J26" t="inlineStr">
         <is>
           <t>Premier international conference; strong malware and reverse engineering tracks with ransomware family content.</t>
@@ -1746,8 +1696,6 @@
           <t>IR case studies, red/blue team techniques, ransomware response</t>
         </is>
       </c>
-      <c r="H27" t="inlineStr"/>
-      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr">
         <is>
           <t>Practitioner-heavy conference with strong IR and blue team focus; good ransomware response content.</t>
@@ -1772,7 +1720,7 @@
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@SecTorCA</t>
+          <t>https://www.youtube.com/channel/UChoKA8GQo6XIRxJOIDE15oA</t>
         </is>
       </c>
       <c r="D28" t="inlineStr">
@@ -1795,8 +1743,6 @@
           <t>Security research talks, IR and threat intelligence sessions</t>
         </is>
       </c>
-      <c r="H28" t="inlineStr"/>
-      <c r="I28" t="inlineStr"/>
       <c r="J28" t="inlineStr">
         <is>
           <t>Canada's premier security conference; enterprise-focused with solid IR and ransomware response content.</t>
@@ -1844,8 +1790,6 @@
           <t>Security research talks, technical deep dives</t>
         </is>
       </c>
-      <c r="H29" t="inlineStr"/>
-      <c r="I29" t="inlineStr"/>
       <c r="J29" t="inlineStr">
         <is>
           <t>Regional conference with growing technical depth; useful supplementary coverage.</t>
@@ -1893,16 +1837,14 @@
           <t>Research-heavy talks, vulnerability and exploitation content</t>
         </is>
       </c>
-      <c r="H30" t="inlineStr"/>
-      <c r="I30" t="inlineStr"/>
       <c r="J30" t="inlineStr">
         <is>
-          <t>Research-heavy conference; useful for exploitation techniques relevant to ransomware initial access.</t>
+          <t>Research-heavy conference; useful for exploitation techniques relevant to ransomware initial access. [EXCLUDED: no dedicated YouTube channel found via API handle lookup or name search as of 2026-08-11 — likely hosted only on other platforms/conference archives.]</t>
         </is>
       </c>
       <c r="K30" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1942,8 +1884,6 @@
           <t>OT/ICS security talks, ransomware impact on industrial systems</t>
         </is>
       </c>
-      <c r="H31" t="inlineStr"/>
-      <c r="I31" t="inlineStr"/>
       <c r="J31" t="inlineStr">
         <is>
           <t>DEF CON village focused on ICS/OT; critical for ransomware-on-industrial-infrastructure coverage not found in mainstream channels.</t>
@@ -1991,16 +1931,14 @@
           <t>European security research, malware and threat intelligence talks</t>
         </is>
       </c>
-      <c r="H32" t="inlineStr"/>
-      <c r="I32" t="inlineStr"/>
       <c r="J32" t="inlineStr">
         <is>
-          <t>Luxembourg-based European conference; strong malware and ransomware research from European practitioners.</t>
+          <t>Luxembourg-based European conference; strong malware and ransomware research from European practitioners. [EXCLUDED: no dedicated YouTube channel found via API handle lookup or name search as of 2026-08-11 — likely hosted only on other platforms/conference archives.]</t>
         </is>
       </c>
       <c r="K32" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2040,8 +1978,6 @@
           <t>Enterprise security research, Active Directory, network defence</t>
         </is>
       </c>
-      <c r="H33" t="inlineStr"/>
-      <c r="I33" t="inlineStr"/>
       <c r="J33" t="inlineStr">
         <is>
           <t>German conference; strong Active Directory and enterprise security content highly relevant to ransomware lateral movement.</t>
@@ -2089,8 +2025,6 @@
           <t>Microsoft-hosted security research talks, ransomware defence</t>
         </is>
       </c>
-      <c r="H34" t="inlineStr"/>
-      <c r="I34" t="inlineStr"/>
       <c r="J34" t="inlineStr">
         <is>
           <t>Microsoft's internal security conference; strong Windows-platform ransomware defence and response content.</t>
@@ -2138,8 +2072,6 @@
           <t>Nation-state actor analysis, ransomware-as-geopolitical-tool</t>
         </is>
       </c>
-      <c r="H35" t="inlineStr"/>
-      <c r="I35" t="inlineStr"/>
       <c r="J35" t="inlineStr">
         <is>
           <t>Focused on nation-state threats; covers ransomware used as geopolitical instrument (e.g. North Korea, Iran) often absent from other channels.</t>
@@ -2187,8 +2119,6 @@
           <t>Exploitation research, low-level vulnerability analysis</t>
         </is>
       </c>
-      <c r="H36" t="inlineStr"/>
-      <c r="I36" t="inlineStr"/>
       <c r="J36" t="inlineStr">
         <is>
           <t>Deep exploitation research; useful for understanding vulnerability classes used in ransomware initial access.</t>
@@ -2213,7 +2143,7 @@
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@Claroty</t>
+          <t>https://www.youtube.com/channel/UC82cIUC3ZzlVjiNvMGe4dHA</t>
         </is>
       </c>
       <c r="D37" t="inlineStr">
@@ -2236,8 +2166,6 @@
           <t>OT/ICS threat briefings, ransomware impact on industrial environments</t>
         </is>
       </c>
-      <c r="H37" t="inlineStr"/>
-      <c r="I37" t="inlineStr"/>
       <c r="J37" t="inlineStr">
         <is>
           <t>OT/ICS security vendor; strong coverage of ransomware hitting manufacturing, energy, and utilities sectors.</t>
@@ -2285,8 +2213,6 @@
           <t>ICS threat intelligence, ransomware in operational technology</t>
         </is>
       </c>
-      <c r="H38" t="inlineStr"/>
-      <c r="I38" t="inlineStr"/>
       <c r="J38" t="inlineStr">
         <is>
           <t>ICS-focused threat intel vendor; covers ransomware targeting operational technology networks.</t>
@@ -2334,8 +2260,6 @@
           <t>ICS security talks, ransomware impact on critical infrastructure</t>
         </is>
       </c>
-      <c r="H39" t="inlineStr"/>
-      <c r="I39" t="inlineStr"/>
       <c r="J39" t="inlineStr">
         <is>
           <t>Premier ICS security conference (Dale Peterson); strong content on ransomware disrupting critical infrastructure — Colonial Pipeline-type incidents.</t>
@@ -2383,8 +2307,6 @@
           <t>Ransomware advisories, government guidance, StopRansomware briefings</t>
         </is>
       </c>
-      <c r="H40" t="inlineStr"/>
-      <c r="I40" t="inlineStr"/>
       <c r="J40" t="inlineStr">
         <is>
           <t>US Cybersecurity and Infrastructure Security Agency; publishes official StopRansomware advisories and briefings — unique government perspective.</t>
@@ -2432,8 +2354,6 @@
           <t>Critical infrastructure defence, air-gap and OT security</t>
         </is>
       </c>
-      <c r="H41" t="inlineStr"/>
-      <c r="I41" t="inlineStr"/>
       <c r="J41" t="inlineStr">
         <is>
           <t>Air-gap and unidirectional gateway vendor; covers ransomware threat to critical infrastructure from a defence architecture perspective.</t>
@@ -2458,7 +2378,7 @@
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@RiskyBusiness</t>
+          <t>https://www.youtube.com/channel/UCZzIaWixWHa96R7K4c40_Dg</t>
         </is>
       </c>
       <c r="D42" t="inlineStr">
@@ -2481,8 +2401,6 @@
           <t>Weekly security news podcast, expert interviews on ransomware incidents</t>
         </is>
       </c>
-      <c r="H42" t="inlineStr"/>
-      <c r="I42" t="inlineStr"/>
       <c r="J42" t="inlineStr">
         <is>
           <t>Top infosec news show (Patrick Gray); ransomware incidents covered in depth with vendor and researcher guests. Lower technical density but strong contextual value.</t>
@@ -2530,8 +2448,6 @@
           <t>Weekly shows with vendor and practitioner guests, threat roundups</t>
         </is>
       </c>
-      <c r="H43" t="inlineStr"/>
-      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr">
         <is>
           <t>Long-running show (Paul Asadoorian); high volume with mixed technical depth — good for incident and actor name coverage.</t>
@@ -2556,7 +2472,7 @@
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@DarknetDiaries</t>
+          <t>https://www.youtube.com/channel/UCMIqrmh2lMdzhlCPK5ahsAg</t>
         </is>
       </c>
       <c r="D44" t="inlineStr">
@@ -2579,8 +2495,6 @@
           <t>Story-driven incident breakdowns, ransomware case narratives</t>
         </is>
       </c>
-      <c r="H44" t="inlineStr"/>
-      <c r="I44" t="inlineStr"/>
       <c r="J44" t="inlineStr">
         <is>
           <t>Jack Rhysider; narrative-style incident breakdowns including ransomware cases. Lower technical density but strong for actor name and family coverage.</t>
@@ -2605,7 +2519,7 @@
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>https://www.youtube.com/@cyb3rops</t>
+          <t>https://www.youtube.com/channel/UC9lFYoA9MAFhnAzX-AtXFxw</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
@@ -2628,8 +2542,6 @@
           <t>YARA rule writing, Sigma detection, threat hunting</t>
         </is>
       </c>
-      <c r="H45" t="inlineStr"/>
-      <c r="I45" t="inlineStr"/>
       <c r="J45" t="inlineStr">
         <is>
           <t>Author of YARA and key Sigma rules for ransomware detection; content highly aligned with detection engineering for ransomware IoCs.</t>
@@ -2677,16 +2589,14 @@
           <t>DFIR tooling walkthroughs — KAPE, Timeline Explorer, artefact analysis</t>
         </is>
       </c>
-      <c r="H46" t="inlineStr"/>
-      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr">
         <is>
-          <t>Creator of KAPE and other DFIR tools widely used in ransomware incident response; tooling content directly relevant to ransomware artefact collection.</t>
+          <t>Creator of KAPE and other DFIR tools widely used in ransomware incident response; tooling content directly relevant to ransomware artefact collection. [EXCLUDED: no dedicated YouTube channel found via API handle lookup or name search as of 2026-08-11 — likely hosted only on other platforms/conference archives.]</t>
         </is>
       </c>
       <c r="K46" t="inlineStr">
         <is>
-          <t>Yes</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -2726,8 +2636,6 @@
           <t>SOC training, ransomware investigation labs, blue team walkthroughs</t>
         </is>
       </c>
-      <c r="H47" t="inlineStr"/>
-      <c r="I47" t="inlineStr"/>
       <c r="J47" t="inlineStr">
         <is>
           <t>SOC training platform with ransomware investigation scenario content; useful for detection and response language coverage.</t>
@@ -2750,17 +2658,11 @@
           <t>Active Countermeasures (already C43)</t>
         </is>
       </c>
-      <c r="C48" t="inlineStr"/>
       <c r="D48" t="inlineStr">
         <is>
           <t>— duplicate, already in Batch 1 —</t>
         </is>
       </c>
-      <c r="E48" t="inlineStr"/>
-      <c r="F48" t="inlineStr"/>
-      <c r="G48" t="inlineStr"/>
-      <c r="H48" t="inlineStr"/>
-      <c r="I48" t="inlineStr"/>
       <c r="J48" t="inlineStr">
         <is>
           <t>Duplicate check placeholder — remove or replace with new candidate before finalising.</t>
@@ -2808,8 +2710,6 @@
           <t>IR case studies, threat briefings, ransomware response</t>
         </is>
       </c>
-      <c r="H49" t="inlineStr"/>
-      <c r="I49" t="inlineStr"/>
       <c r="J49" t="inlineStr">
         <is>
           <t>Security consulting firm with dedicated ransomware response practice; regular threat intelligence and IR content.</t>
@@ -2857,8 +2757,6 @@
           <t>Threat intel platform content, actor profiling, IOC analysis</t>
         </is>
       </c>
-      <c r="H50" t="inlineStr"/>
-      <c r="I50" t="inlineStr"/>
       <c r="J50" t="inlineStr">
         <is>
           <t>TIP vendor with regular threat briefings including ransomware actor and campaign coverage.</t>
@@ -2906,8 +2804,6 @@
           <t>IR case studies, threat briefings, ransomware trends</t>
         </is>
       </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
       <c r="J51" t="inlineStr">
         <is>
           <t>Large security integrator with IR practice; publishes ransomware response and preparedness content.</t>
@@ -2955,8 +2851,6 @@
           <t>Exploitation research, vulnerability analysis, security research talks</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr"/>
-      <c r="I52" t="inlineStr"/>
       <c r="J52" t="inlineStr">
         <is>
           <t>Pacific-rim conference; strong exploitation and vulnerability research useful for ransomware initial access context.</t>
